--- a/artfynd/A 34784-2025 artfynd.xlsx
+++ b/artfynd/A 34784-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>127013880</v>
       </c>
       <c r="B3" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>127013887</v>
       </c>
       <c r="B4" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>127013884</v>
       </c>
       <c r="B5" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>127013886</v>
       </c>
       <c r="B6" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>127013881</v>
       </c>
       <c r="B7" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         <v>127013892</v>
       </c>
       <c r="B8" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>127013890</v>
       </c>
       <c r="B9" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>127013889</v>
       </c>
       <c r="B10" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>127013882</v>
       </c>
       <c r="B11" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         <v>127013891</v>
       </c>
       <c r="B12" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>127013885</v>
       </c>
       <c r="B13" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 34784-2025 artfynd.xlsx
+++ b/artfynd/A 34784-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>127013880</v>
       </c>
       <c r="B3" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>127013887</v>
       </c>
       <c r="B4" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>127013884</v>
       </c>
       <c r="B5" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>127013886</v>
       </c>
       <c r="B6" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>127013881</v>
       </c>
       <c r="B7" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         <v>127013892</v>
       </c>
       <c r="B8" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>127013890</v>
       </c>
       <c r="B9" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>127013889</v>
       </c>
       <c r="B10" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>127013882</v>
       </c>
       <c r="B11" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         <v>127013891</v>
       </c>
       <c r="B12" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>127013885</v>
       </c>
       <c r="B13" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 34784-2025 artfynd.xlsx
+++ b/artfynd/A 34784-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>127013880</v>
       </c>
       <c r="B3" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>127013887</v>
       </c>
       <c r="B4" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>127013884</v>
       </c>
       <c r="B5" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>127013886</v>
       </c>
       <c r="B6" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>127013881</v>
       </c>
       <c r="B7" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         <v>127013892</v>
       </c>
       <c r="B8" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>127013890</v>
       </c>
       <c r="B9" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>127013889</v>
       </c>
       <c r="B10" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>127013882</v>
       </c>
       <c r="B11" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         <v>127013891</v>
       </c>
       <c r="B12" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>127013885</v>
       </c>
       <c r="B13" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 34784-2025 artfynd.xlsx
+++ b/artfynd/A 34784-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>127013880</v>
       </c>
       <c r="B3" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>127013887</v>
       </c>
       <c r="B4" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>127013884</v>
       </c>
       <c r="B5" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1100,7 +1100,7 @@
         <v>127013886</v>
       </c>
       <c r="B6" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
         <v>127013881</v>
       </c>
       <c r="B7" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
         <v>127013892</v>
       </c>
       <c r="B8" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
         <v>127013890</v>
       </c>
       <c r="B9" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         <v>127013889</v>
       </c>
       <c r="B10" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>127013882</v>
       </c>
       <c r="B11" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
         <v>127013891</v>
       </c>
       <c r="B12" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>127013885</v>
       </c>
       <c r="B13" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 34784-2025 artfynd.xlsx
+++ b/artfynd/A 34784-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1997210</v>
+        <v>1871744</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>512452.9245541566</v>
+        <v>512450</v>
       </c>
       <c r="R2" t="n">
-        <v>7145034.030740156</v>
+        <v>7145010</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2012-09-25</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2012-09-25</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127013880</v>
+        <v>1997210</v>
       </c>
       <c r="B3" t="n">
-        <v>57672</v>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,37 +787,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Fånsjön, Jmt</t>
+          <t>Norr om Fånsjön, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>512392</v>
+        <v>512453</v>
       </c>
       <c r="R3" t="n">
-        <v>7145097</v>
+        <v>7145034</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -856,17 +841,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-07-26</t>
+          <t>2012-09-25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-07-26</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>2012-09-25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -881,22 +861,26 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>SCA Naturvärdesinventeringar</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Hugo Ström</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127013887</v>
+        <v>1997211</v>
       </c>
       <c r="B4" t="n">
-        <v>57672</v>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,37 +888,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Fånsjön, Jmt</t>
+          <t>Norr om Fånsjön, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>512465</v>
+        <v>512559</v>
       </c>
       <c r="R4" t="n">
-        <v>7145392</v>
+        <v>7144980</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -958,17 +942,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-07-26</t>
+          <t>2012-09-25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-07-26</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+          <t>2012-09-25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -983,22 +962,26 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>SCA Naturvärdesinventeringar</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Hugo Ström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127013884</v>
+        <v>127013880</v>
       </c>
       <c r="B5" t="n">
-        <v>57672</v>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1030,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>512451</v>
+        <v>512392</v>
       </c>
       <c r="R5" t="n">
-        <v>7145225</v>
+        <v>7145097</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1070,7 +1053,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1097,10 +1080,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127013886</v>
+        <v>127013881</v>
       </c>
       <c r="B6" t="n">
-        <v>57672</v>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1132,10 +1115,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>512451</v>
+        <v>512429</v>
       </c>
       <c r="R6" t="n">
-        <v>7145294</v>
+        <v>7145173</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1199,10 +1182,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127013881</v>
+        <v>127013882</v>
       </c>
       <c r="B7" t="n">
-        <v>57672</v>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1234,10 +1217,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>512429</v>
+        <v>512489</v>
       </c>
       <c r="R7" t="n">
-        <v>7145173</v>
+        <v>7145208</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1301,10 +1284,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127013892</v>
+        <v>127013884</v>
       </c>
       <c r="B8" t="n">
-        <v>57672</v>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1336,10 +1319,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>512478</v>
+        <v>512451</v>
       </c>
       <c r="R8" t="n">
-        <v>7145379</v>
+        <v>7145225</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1403,10 +1386,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127013890</v>
+        <v>127013885</v>
       </c>
       <c r="B9" t="n">
-        <v>57672</v>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1438,10 +1421,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>512442</v>
+        <v>512470</v>
       </c>
       <c r="R9" t="n">
-        <v>7145423</v>
+        <v>7145266</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1505,10 +1488,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127013889</v>
+        <v>127013886</v>
       </c>
       <c r="B10" t="n">
-        <v>57672</v>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1540,10 +1523,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>512444</v>
+        <v>512451</v>
       </c>
       <c r="R10" t="n">
-        <v>7145416</v>
+        <v>7145294</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1607,10 +1590,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127013882</v>
+        <v>127013887</v>
       </c>
       <c r="B11" t="n">
-        <v>57672</v>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1642,10 +1625,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>512489</v>
+        <v>512465</v>
       </c>
       <c r="R11" t="n">
-        <v>7145208</v>
+        <v>7145392</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1682,7 +1665,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1709,10 +1692,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127013891</v>
+        <v>127013889</v>
       </c>
       <c r="B12" t="n">
-        <v>57672</v>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1744,10 +1727,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>512438</v>
+        <v>512444</v>
       </c>
       <c r="R12" t="n">
-        <v>7145428</v>
+        <v>7145416</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1784,7 +1767,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1811,10 +1794,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127013885</v>
+        <v>127013890</v>
       </c>
       <c r="B13" t="n">
-        <v>57672</v>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1846,10 +1829,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>512470</v>
+        <v>512442</v>
       </c>
       <c r="R13" t="n">
-        <v>7145266</v>
+        <v>7145423</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1910,6 +1893,210 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>127013891</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Fånsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>512438</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7145428</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Alanäs</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>127013892</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Fånsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>512478</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7145379</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Alanäs</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-07-26</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 34784-2025 artfynd.xlsx
+++ b/artfynd/A 34784-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1871744</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1997210</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1997211</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1077,6 +1097,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127013880</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1179,6 +1204,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127013881</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1281,6 +1311,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127013882</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1383,6 +1418,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127013884</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1485,6 +1525,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127013885</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1587,6 +1632,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127013886</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1689,6 +1739,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127013887</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1791,6 +1846,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127013889</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1893,6 +1953,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127013890</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1995,6 +2060,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127013891</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2097,8 +2167,29 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127013892</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>